--- a/Sorting_types/sorting data.xlsx
+++ b/Sorting_types/sorting data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Sorting_types\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B526A41-6922-4E4A-80B2-01CA8C46EB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F17DB7B-2493-4F50-93FF-4863AB44220F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D887F24B-B128-4729-9C42-8F01CAE313B6}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>arr[0]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,6 +89,10 @@
   </si>
   <si>
     <t>0~7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i最大7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,12 +458,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A2EBF5-BA7C-4C6D-BFCE-8A008DFBCAE6}">
-  <dimension ref="A9:J16"/>
+  <dimension ref="A7:J16"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>0</v>
